--- a/introducao-economia-IFB/aulas/outros_arquivos/Ementa ampliada.xlsx
+++ b/introducao-economia-IFB/aulas/outros_arquivos/Ementa ampliada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adm\Desktop\Site_Aula\introducao-economia-IFB\aulas\outros_arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB716FAF-0822-4407-9DFF-8F15863F7AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BC1F37-D83F-44AB-9E70-15E638ABA491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C3FD7EA0-250E-4EBE-82D4-1D63064845E7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
   <si>
     <t>Unidade</t>
   </si>
@@ -45,21 +45,12 @@
     <t>Microtema</t>
   </si>
   <si>
-    <t>Tópicos em microeconomia</t>
-  </si>
-  <si>
     <t>Leitura</t>
   </si>
   <si>
     <t>Temas e conceitos</t>
   </si>
   <si>
-    <t>Introdução</t>
-  </si>
-  <si>
-    <t>Dez Princípios de economia, divididos em três ideias:                                                                                                                                                                                                                                                             1) como as pessoas tomam decisões (trade-off, custo de oportunidade, decisões na margem, incentivos);                                                                                                                                               2) como as pessoas interagem (comércio, mercados e governo); e                                                                                                                                                                                                                                                 3) Como a economia funciona (produtividade, preços, inflação e desemprego).</t>
-  </si>
-  <si>
     <t>Avaliação</t>
   </si>
   <si>
@@ -72,9 +63,6 @@
     <t>Firma</t>
   </si>
   <si>
-    <t>1º Controle</t>
-  </si>
-  <si>
     <t>1ª Prova</t>
   </si>
   <si>
@@ -96,15 +84,9 @@
     <t>Aula assíncrona</t>
   </si>
   <si>
-    <t>Segunda-feira</t>
-  </si>
-  <si>
     <t>sexta-feira</t>
   </si>
   <si>
-    <t>Pensando como um economista.                                                                                              Método científico, modelos.                                                                                                        Análise normativa e análise positiva.                                                                                       Fronteira de possibilidade de produção.                                                           Microeconomia e macroeconomia.Interdependência e ganhos comerciais.                                                                                Vantagem absoluta e vantagem comparativa.</t>
-  </si>
-  <si>
     <t>Assíncrona</t>
   </si>
   <si>
@@ -117,9 +99,6 @@
     <t>Revisão e Exercício</t>
   </si>
   <si>
-    <t>Revisão para a turma de sexta e aula para a de segunda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Determinantes e aplicações.                                                                                                                Uso do modelo de equilíbrio parcial para análise de políticas de governo.Mercados e bem-estar.                                                                                                              Excedente do consumidor e do produtor.                                                                             Eficiência de mercado.                                                                                                                  Teoremas de bem-estar e falhas de mercado. </t>
   </si>
   <si>
@@ -132,9 +111,6 @@
     <t>Prova Final</t>
   </si>
   <si>
-    <t>Prova Substitutiva</t>
-  </si>
-  <si>
     <t>Oferta, demanda e elasticidade</t>
   </si>
   <si>
@@ -144,9 +120,6 @@
     <t>Custos, firma competitiva e estruturas de mercado</t>
   </si>
   <si>
-    <t>Listas e revisão</t>
-  </si>
-  <si>
     <t>Aulas 1 a 4</t>
   </si>
   <si>
@@ -159,12 +132,6 @@
     <t>Unid. 4 a 6</t>
   </si>
   <si>
-    <t>Todo o semestre</t>
-  </si>
-  <si>
-    <t>Revisão para a turma de segunda e aula para a de sexta</t>
-  </si>
-  <si>
     <t>Lista de exercícios 2</t>
   </si>
   <si>
@@ -172,6 +139,24 @@
   </si>
   <si>
     <t>3º Controle</t>
+  </si>
+  <si>
+    <t>Dez Princípios de economia, divididos em três ideias:                                                                                                                                                                                                                                                             1) como as pessoas tomam decisões (trade-off, custo de oportunidade, decisões na margem, incentivos);                                                                                                                                               2) como as pessoas interagem (comércio, mercados e governo); e         Pensando como um economista.                                                                                              Método científico, modelos.                                                                                                        Análise normativa e análise positiva.                                                                                       Fronteira de possibilidade de produção.                                                           Microeconomia e macroeconomia.Interdependência e ganhos comerciais.                                                                                Vantagem absoluta e vantagem comparativa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1º Controle </t>
+  </si>
+  <si>
+    <t>Atividade Assíncrona</t>
+  </si>
+  <si>
+    <t>5º Controle</t>
+  </si>
+  <si>
+    <t>4º Controle</t>
+  </si>
+  <si>
+    <t>2ª Prova</t>
   </si>
 </sst>
 </file>
@@ -181,7 +166,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +204,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -246,29 +238,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -277,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -313,46 +287,49 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -668,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5353277A-22FD-42C8-8B3B-134AF19D686D}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6"/>
@@ -685,13 +662,13 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -703,503 +680,374 @@
         <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:10" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>46300</v>
+        <v>46304</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>46305</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="20">
-        <v>1</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="I3" s="21"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>46311</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="21">
+        <v>2</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>46304</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>46305</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B5" s="6">
         <v>2</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="20">
-        <v>2</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="22"/>
-      <c r="F5" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="22"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="111" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>46312</v>
+        <v>46318</v>
       </c>
       <c r="B6" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="20"/>
+        <v>16</v>
+      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="27"/>
+      <c r="G6" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>32</v>
+      </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>46314</v>
-      </c>
-      <c r="B7" s="6">
-        <v>3</v>
+        <v>46319</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="20"/>
+        <v>18</v>
+      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G7" s="21"/>
+      <c r="H7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>46318</v>
-      </c>
-      <c r="B8" s="6">
+        <v>46325</v>
+      </c>
+      <c r="B8" s="17">
+        <v>4</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="21">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="20"/>
       <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="20"/>
+        <v>18</v>
+      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="20"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="225" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="137.25" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>46321</v>
+        <v>46332</v>
       </c>
       <c r="B10" s="6">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="11">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="20">
-        <v>3</v>
-      </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="25" t="s">
+      <c r="E10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="27">
+        <v>46333</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>46325</v>
-      </c>
-      <c r="B11" s="6">
-        <v>4</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="23"/>
+      <c r="E11" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="14" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>46326</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>23</v>
+        <v>46339</v>
+      </c>
+      <c r="B12" s="6">
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" spans="1:10" ht="137.25" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>46332</v>
+        <v>46340</v>
       </c>
       <c r="B13" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="11">
-        <v>4</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>46333</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>46347</v>
+      </c>
+      <c r="B14" s="6">
+        <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="137.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="I14" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
-        <v>46335</v>
+        <v>46353</v>
       </c>
       <c r="B15" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="6">
-        <v>4</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
+        <v>16</v>
+      </c>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
-        <v>46339</v>
+        <v>46354</v>
       </c>
       <c r="B16" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="I16" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>46340</v>
+        <v>46360</v>
       </c>
       <c r="B17" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="24"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="27">
+        <v>46361</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="I17" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>46342</v>
-      </c>
-      <c r="B18" s="6">
-        <v>7</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="I18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>46347</v>
-      </c>
-      <c r="B19" s="6">
-        <v>7</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="18"/>
-      <c r="I19" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>46349</v>
-      </c>
-      <c r="B20" s="6">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>46353</v>
-      </c>
-      <c r="B21" s="6">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>46354</v>
-      </c>
-      <c r="B22" s="6">
-        <v>9</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="I22" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>46360</v>
-      </c>
-      <c r="B23" s="6">
-        <v>9</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="18"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>46361</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="18"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>46333</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="D18" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E18" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="29"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>46367</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="G2:G4"/>
+  <mergeCells count="13">
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="E12:E17"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="E2:E9"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G2:G3"/>
     <mergeCell ref="I2:I3"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="D5:D9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="E15:E24"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
